--- a/etf_holdings/2026-10-20_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:05</t>
+          <t>2026-10-20 21:54:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,38 +504,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.85%1380</t>
+          <t>+1.37%6650</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.85%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1380</v>
+        <v>6650</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.90%1,299,000</t>
+          <t>7.82%260,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.90%</t>
+          <t>7.82%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1299000</v>
+        <v>260000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:05</t>
+          <t>2026-10-20 21:54:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.75%1120</t>
+          <t>-5.43%1305</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+2.75%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1120</v>
+        <v>1305</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.55%1,530,000</t>
+          <t>7.67%1,299,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.55%</t>
+          <t>7.67%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1530000</v>
+        <v>1299000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:05</t>
+          <t>2026-10-20 21:54:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.53%6560</t>
+          <t>-5.8%1055</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6560</v>
+        <v>1055</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.51%260,000</t>
+          <t>7.30%1,530,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.51%</t>
+          <t>7.30%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>260000</v>
+        <v>1530000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:05</t>
+          <t>2026-10-20 21:54:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.58%5235</t>
+          <t>-6.4%4900</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5235</v>
+        <v>4900</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.45%323,000</t>
+          <t>7.16%323,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.45%</t>
+          <t>7.16%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:05</t>
+          <t>2026-10-20 21:54:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.4%1250</t>
+          <t>-1.09%7745</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1250</v>
+        <v>7745</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.21%1,127,000</t>
+          <t>6.06%173,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.21%</t>
+          <t>6.06%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1127000</v>
+        <v>173000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:05</t>
+          <t>2026-10-20 21:54:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+4.68%7830</t>
+          <t>-5.2%1185</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+4.68%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7830</v>
+        <v>1185</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.97%173,000</t>
+          <t>6.04%1,127,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.97%</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>173000</v>
+        <v>1127000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:05</t>
+          <t>2026-10-20 21:54:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.99%1975</t>
+          <t>-2.53%1925</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-2.53%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1975</v>
+        <v>1925</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:05</t>
+          <t>2026-10-20 21:54:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.03%15980</t>
+          <t>-0.5%15900</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.03%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>15980</v>
+        <v>15900</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.58%79,300</t>
+          <t>5.70%79,300</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.58%</t>
+          <t>5.70%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:05</t>
+          <t>2026-10-20 21:54:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.06%4205</t>
+          <t>-1.31%4150</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4205</v>
+        <v>4150</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.45%294,000</t>
+          <t>5.52%294,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.45%</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:05</t>
+          <t>2026-10-20 21:54:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.26%2005</t>
+          <t>-1.75%1970</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2005</v>
+        <v>1970</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.38%609,000</t>
+          <t>5.43%609,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.38%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:05</t>
+          <t>2026-10-20 21:54:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.77%5125</t>
+          <t>-3.51%4945</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5125</v>
+        <v>4945</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.79%212,000</t>
+          <t>4.74%212,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.79%</t>
+          <t>4.74%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:05</t>
+          <t>2026-10-20 21:54:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.15%3320</t>
+          <t>+0.15%3325</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1189,16 +1189,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3320</v>
+        <v>3325</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.07%278,000</t>
+          <t>4.18%278,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:05</t>
+          <t>2026-10-20 21:54:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-6.92%821</t>
+          <t>-2.56%800</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.92%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>821</v>
+        <v>800</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.72%1,030,000</t>
+          <t>3.73%1,030,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.73%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:05</t>
+          <t>2026-10-20 21:54:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+3.78%2335</t>
+          <t>-1.93%2290</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+3.78%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2335</v>
+        <v>2290</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.51%341,000</t>
+          <t>3.53%341,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.53%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:05</t>
+          <t>2026-10-20 21:54:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+2.18%5400</t>
+          <t>-3.61%5205</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-3.61%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5400</v>
+        <v>5205</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.85%120,000</t>
+          <t>2.83%120,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:06</t>
+          <t>2026-10-20 21:54:42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.93%1630</t>
+          <t>+1.81%10100</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>+1.81%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1630</v>
+        <v>10100</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.20%306,000</t>
+          <t>2.28%50,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>306000</v>
+        <v>50000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:06</t>
+          <t>2026-10-20 21:54:42</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.35%9920</t>
+          <t>-4.91%1550</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>9920</v>
+        <v>1550</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.18%50,000</t>
+          <t>2.15%306,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>50000</v>
+        <v>306000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:06</t>
+          <t>2026-10-20 21:54:42</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0%2420</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.91%179,000</t>
+          <t>1.95%179,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:06</t>
+          <t>2026-10-20 21:54:42</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.87%1525</t>
+          <t>+1.31%1545</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.87%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1525</v>
+        <v>1545</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.34%200,000</t>
+          <t>1.40%200,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:06</t>
+          <t>2026-10-20 21:54:42</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.35%1405</t>
+          <t>-6.05%1320</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-6.05%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1405</v>
+        <v>1320</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.92%148,000</t>
+          <t>0.88%148,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:06</t>
+          <t>2026-10-20 21:54:42</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+2.17%1885</t>
+          <t>+2.12%1925</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1885</v>
+        <v>1925</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.82%99,139</t>
+          <t>0.86%99,139</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:06</t>
+          <t>2026-10-20 21:54:42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.31%1640</t>
+          <t>-2.13%1605</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-2.13%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1640</v>
+        <v>1605</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:06</t>
+          <t>2026-10-20 21:54:42</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>6526達發</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0%5160</t>
+          <t>+2.56%801</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.56%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5160</v>
+        <v>801</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.52%23,000</t>
+          <t>0.53%146,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>23000</v>
+        <v>146000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:06</t>
+          <t>2026-10-20 21:54:42</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6526達發</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.26%781</t>
+          <t>-3.88%4960</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-3.88%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>781</v>
+        <v>4960</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.50%146,000</t>
+          <t>0.52%23,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>146000</v>
+        <v>23000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:06</t>
+          <t>2026-10-20 21:54:42</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.8%982</t>
+          <t>-3.77%945</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-3.77%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>982</v>
+        <v>945</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.22%50,000</t>
+          <t>0.21%50,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:06</t>
+          <t>2026-10-20 21:54:42</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.39%163.5</t>
+          <t>-2.14%160</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.39%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>163.5</v>
+        <v>160</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:06</t>
+          <t>2026-10-20 21:54:42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-3.33%246.5</t>
+          <t>+0.41%247.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>246.5</v>
+        <v>247.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:06</t>
+          <t>2026-10-20 21:54:42</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-4.18%263.5</t>
+          <t>-1.52%259.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.18%</t>
+          <t>-1.52%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>263.5</v>
+        <v>259.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:06</t>
+          <t>2026-10-20 21:54:42</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.19%258</t>
+          <t>-4.26%247</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-4.26%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:06</t>
+          <t>2026-10-20 21:54:42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.42%6245</t>
+          <t>-4.32%5975</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-4.32%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>6245</v>
+        <v>5975</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:07</t>
+          <t>2026-10-20 21:54:43</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+5.26%520</t>
+          <t>-5.96%489</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+5.26%</t>
+          <t>-5.96%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>520</v>
+        <v>489</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:07</t>
+          <t>2026-10-20 21:54:43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.81%3715</t>
+          <t>-2.02%3640</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>-2.02%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3715</v>
+        <v>3640</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:07</t>
+          <t>2026-10-20 21:54:43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.13%131.5</t>
+          <t>-3.42%127</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>131.5</v>
+        <v>127</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:07</t>
+          <t>2026-10-20 21:54:43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.88%679</t>
+          <t>+0.74%684</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.01%5,000</t>
+          <t>0.02%5,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:07</t>
+          <t>2026-10-20 21:54:43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.76%3175</t>
+          <t>-2.52%3095</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3175</v>
+        <v>3095</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:07</t>
+          <t>2026-10-20 21:54:43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.02%289.5</t>
+          <t>-0.52%288</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.02%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>289.5</v>
+        <v>288</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:07</t>
+          <t>2026-10-20 21:54:43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-5.62%1175</t>
+          <t>-1.7%1155</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.62%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1175</v>
+        <v>1155</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:07</t>
+          <t>2026-10-20 21:54:43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.84%444</t>
+          <t>-3.04%430.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-3.04%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>444</v>
+        <v>430.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:07</t>
+          <t>2026-10-20 21:54:43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.15%670</t>
+          <t>-1.49%660</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:07</t>
+          <t>2026-10-20 21:54:43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.55%1815</t>
+          <t>-0.55%1805</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1815</v>
+        <v>1805</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:07</t>
+          <t>2026-10-20 21:54:43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-3.45%168</t>
+          <t>-1.19%166</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:07</t>
+          <t>2026-10-20 21:54:43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.14%303.5</t>
+          <t>-2.47%296</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-2.47%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>303.5</v>
+        <v>296</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:07</t>
+          <t>2026-10-20 21:54:43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-4.81%1385</t>
+          <t>-3.97%1330</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-4.81%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1385</v>
+        <v>1330</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:07</t>
+          <t>2026-10-20 21:54:43</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.87%1165</t>
+          <t>-4.72%1110</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-4.72%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1165</v>
+        <v>1110</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 00:30:07</t>
+          <t>2026-10-20 21:54:43</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.84%102.5</t>
+          <t>-3.32%99.1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-3.32%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>102.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-20_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:40</t>
+          <t>2026-10-20 22:20:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:40</t>
+          <t>2026-10-20 22:20:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:40</t>
+          <t>2026-10-20 22:20:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:40</t>
+          <t>2026-10-20 22:20:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:40</t>
+          <t>2026-10-20 22:20:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:40</t>
+          <t>2026-10-20 22:20:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:40</t>
+          <t>2026-10-20 22:20:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:40</t>
+          <t>2026-10-20 22:20:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:40</t>
+          <t>2026-10-20 22:20:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:40</t>
+          <t>2026-10-20 22:20:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:40</t>
+          <t>2026-10-20 22:20:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:40</t>
+          <t>2026-10-20 22:20:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:40</t>
+          <t>2026-10-20 22:20:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:40</t>
+          <t>2026-10-20 22:20:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:40</t>
+          <t>2026-10-20 22:20:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:42</t>
+          <t>2026-10-20 22:20:31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:42</t>
+          <t>2026-10-20 22:20:31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:42</t>
+          <t>2026-10-20 22:20:31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:42</t>
+          <t>2026-10-20 22:20:31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:42</t>
+          <t>2026-10-20 22:20:31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:42</t>
+          <t>2026-10-20 22:20:31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:42</t>
+          <t>2026-10-20 22:20:31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:42</t>
+          <t>2026-10-20 22:20:31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:42</t>
+          <t>2026-10-20 22:20:31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:42</t>
+          <t>2026-10-20 22:20:31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:42</t>
+          <t>2026-10-20 22:20:31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:42</t>
+          <t>2026-10-20 22:20:31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:42</t>
+          <t>2026-10-20 22:20:31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:42</t>
+          <t>2026-10-20 22:20:31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:42</t>
+          <t>2026-10-20 22:20:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:43</t>
+          <t>2026-10-20 22:20:33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:43</t>
+          <t>2026-10-20 22:20:33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:43</t>
+          <t>2026-10-20 22:20:33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:43</t>
+          <t>2026-10-20 22:20:33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:43</t>
+          <t>2026-10-20 22:20:33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:43</t>
+          <t>2026-10-20 22:20:33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:43</t>
+          <t>2026-10-20 22:20:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:43</t>
+          <t>2026-10-20 22:20:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:43</t>
+          <t>2026-10-20 22:20:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:43</t>
+          <t>2026-10-20 22:20:33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:43</t>
+          <t>2026-10-20 22:20:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:43</t>
+          <t>2026-10-20 22:20:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:43</t>
+          <t>2026-10-20 22:20:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:43</t>
+          <t>2026-10-20 22:20:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:43</t>
+          <t>2026-10-20 22:20:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
